--- a/experiments/results/resnet_imagenet50/ImageNet-1K/ReAct/adaptive/avg/results.xlsx
+++ b/experiments/results/resnet_imagenet50/ImageNet-1K/ReAct/adaptive/avg/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -577,6 +577,43 @@
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>p=None,ash_p=None,rt=1.0,st=0.1,t=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>95.79000000000001</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.1,type=avg</t>
         </is>
       </c>
     </row>
